--- a/outputs/player_points_breakdown.xlsx
+++ b/outputs/player_points_breakdown.xlsx
@@ -1032,19 +1032,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D23" t="n">
-        <v>307</v>
+        <v>274</v>
       </c>
       <c r="E23" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="F23" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G23" t="n">
-        <v>646</v>
+        <v>539</v>
       </c>
     </row>
     <row r="24">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -1068,10 +1068,10 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G24" t="n">
-        <v>157</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>16</v>
       </c>
       <c r="F25" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G25" t="n">
-        <v>290</v>
+        <v>258</v>
       </c>
     </row>
     <row r="26">
@@ -1116,13 +1116,13 @@
         <v>18</v>
       </c>
       <c r="D26" t="n">
-        <v>-14</v>
+        <v>-10</v>
       </c>
       <c r="E26" t="n">
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G26" t="n">
         <v>32</v>
@@ -1140,19 +1140,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="F27" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G27" t="n">
-        <v>384</v>
+        <v>328</v>
       </c>
     </row>
     <row r="28">
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>813</v>
+        <v>726</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1230,10 +1230,10 @@
         <v>34</v>
       </c>
       <c r="F30" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G30" t="n">
-        <v>903</v>
+        <v>812</v>
       </c>
     </row>
     <row r="31">
@@ -1251,16 +1251,16 @@
         <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>256</v>
+        <v>177</v>
       </c>
       <c r="E31" t="n">
         <v>16</v>
       </c>
       <c r="F31" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G31" t="n">
-        <v>323</v>
+        <v>240</v>
       </c>
     </row>
     <row r="32">
@@ -1278,16 +1278,16 @@
         <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>371</v>
+        <v>284</v>
       </c>
       <c r="E32" t="n">
         <v>6</v>
       </c>
       <c r="F32" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G32" t="n">
-        <v>427</v>
+        <v>336</v>
       </c>
     </row>
     <row r="33">
@@ -1305,16 +1305,16 @@
         <v>22</v>
       </c>
       <c r="D33" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E33" t="n">
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G33" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34">
@@ -1332,16 +1332,16 @@
         <v>-2</v>
       </c>
       <c r="D34" t="n">
-        <v>283</v>
+        <v>233</v>
       </c>
       <c r="E34" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="F34" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G34" t="n">
-        <v>349</v>
+        <v>279</v>
       </c>
     </row>
     <row r="35">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -1473,10 +1473,10 @@
         <v>8</v>
       </c>
       <c r="F39" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G39" t="n">
-        <v>79</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40">
@@ -1497,13 +1497,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F40" t="n">
         <v>44</v>
       </c>
       <c r="G40" t="n">
-        <v>415</v>
+        <v>403</v>
       </c>
     </row>
     <row r="41">
@@ -1551,13 +1551,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F42" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G42" t="n">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="43">
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>430</v>
+        <v>343</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F64" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G64" t="n">
-        <v>550</v>
+        <v>451</v>
       </c>
     </row>
     <row r="65">
@@ -2166,19 +2166,19 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D65" t="n">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="E65" t="n">
         <v>84</v>
       </c>
       <c r="F65" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G65" t="n">
-        <v>430</v>
+        <v>395</v>
       </c>
     </row>
     <row r="66">
@@ -2220,19 +2220,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D67" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E67" t="n">
         <v>64</v>
       </c>
       <c r="F67" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G67" t="n">
-        <v>709</v>
+        <v>705</v>
       </c>
     </row>
     <row r="68">
@@ -2247,19 +2247,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="D68" t="n">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="E68" t="n">
         <v>22</v>
       </c>
       <c r="F68" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G68" t="n">
-        <v>357</v>
+        <v>322</v>
       </c>
     </row>
     <row r="69">
@@ -2274,19 +2274,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>494</v>
+        <v>465</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G69" t="n">
-        <v>546</v>
+        <v>505</v>
       </c>
     </row>
     <row r="70">
@@ -2301,19 +2301,19 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D70" t="n">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="E70" t="n">
         <v>38</v>
       </c>
       <c r="F70" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G70" t="n">
-        <v>554</v>
+        <v>558</v>
       </c>
     </row>
     <row r="71">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>32</v>
       </c>
       <c r="F72" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G72" t="n">
-        <v>148</v>
+        <v>109</v>
       </c>
     </row>
     <row r="73">
@@ -2409,19 +2409,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>250</v>
+        <v>214</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F74" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G74" t="n">
-        <v>342</v>
+        <v>294</v>
       </c>
     </row>
     <row r="75">
@@ -2436,19 +2436,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F75" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G75" t="n">
-        <v>549</v>
+        <v>539</v>
       </c>
     </row>
     <row r="76">
@@ -2493,16 +2493,16 @@
         <v>50</v>
       </c>
       <c r="D77" t="n">
-        <v>489</v>
+        <v>464</v>
       </c>
       <c r="E77" t="n">
         <v>24</v>
       </c>
       <c r="F77" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G77" t="n">
-        <v>615</v>
+        <v>586</v>
       </c>
     </row>
     <row r="78">
@@ -2517,19 +2517,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>135</v>
+        <v>83</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G78" t="n">
-        <v>156</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79">
@@ -2544,19 +2544,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G79" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80">
@@ -3246,19 +3246,19 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>393</v>
+        <v>374</v>
       </c>
       <c r="E105" t="n">
         <v>8</v>
       </c>
       <c r="F105" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G105" t="n">
-        <v>447</v>
+        <v>422</v>
       </c>
     </row>
     <row r="106">
@@ -3300,19 +3300,19 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D107" t="n">
-        <v>330</v>
+        <v>297</v>
       </c>
       <c r="E107" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="F107" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G107" t="n">
-        <v>461</v>
+        <v>400</v>
       </c>
     </row>
     <row r="108">
@@ -3327,19 +3327,19 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D108" t="n">
-        <v>208</v>
+        <v>160</v>
       </c>
       <c r="E108" t="n">
         <v>8</v>
       </c>
       <c r="F108" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G108" t="n">
-        <v>278</v>
+        <v>216</v>
       </c>
     </row>
     <row r="109">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>275</v>
+        <v>224</v>
       </c>
       <c r="D110" t="n">
         <v>90</v>
@@ -3390,10 +3390,10 @@
         <v>16</v>
       </c>
       <c r="F110" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G110" t="n">
-        <v>421</v>
+        <v>366</v>
       </c>
     </row>
     <row r="111">
@@ -3543,19 +3543,19 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="F116" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G116" t="n">
-        <v>553</v>
+        <v>526</v>
       </c>
     </row>
     <row r="117">
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>631</v>
+        <v>616</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -3660,10 +3660,10 @@
         <v>76</v>
       </c>
       <c r="F120" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G120" t="n">
-        <v>755</v>
+        <v>736</v>
       </c>
     </row>
     <row r="121">
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -3687,10 +3687,10 @@
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G121" t="n">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="122">
@@ -3714,10 +3714,10 @@
         <v>8</v>
       </c>
       <c r="F122" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G122" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="123">
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>356</v>
+        <v>275</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
@@ -3741,10 +3741,10 @@
         <v>24</v>
       </c>
       <c r="F123" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G123" t="n">
-        <v>432</v>
+        <v>347</v>
       </c>
     </row>
     <row r="124">
@@ -3786,19 +3786,19 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D125" t="n">
-        <v>302</v>
+        <v>254</v>
       </c>
       <c r="E125" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G125" t="n">
-        <v>366</v>
+        <v>297</v>
       </c>
     </row>
     <row r="126">
@@ -3840,19 +3840,19 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="F127" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G127" t="n">
-        <v>629</v>
+        <v>606</v>
       </c>
     </row>
     <row r="128">
@@ -3867,19 +3867,19 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>195</v>
+        <v>145</v>
       </c>
       <c r="D128" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="E128" t="n">
         <v>16</v>
       </c>
       <c r="F128" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G128" t="n">
-        <v>289</v>
+        <v>206</v>
       </c>
     </row>
     <row r="129">
@@ -4464,16 +4464,16 @@
         <v>2</v>
       </c>
       <c r="D150" t="n">
-        <v>367</v>
+        <v>299</v>
       </c>
       <c r="E150" t="n">
         <v>8</v>
       </c>
       <c r="F150" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G150" t="n">
-        <v>421</v>
+        <v>349</v>
       </c>
     </row>
     <row r="151">
@@ -4488,19 +4488,19 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>376</v>
+        <v>354</v>
       </c>
       <c r="D151" t="n">
         <v>25</v>
       </c>
       <c r="E151" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="F151" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G151" t="n">
-        <v>541</v>
+        <v>507</v>
       </c>
     </row>
     <row r="152">
@@ -4515,19 +4515,19 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>613</v>
+        <v>562</v>
       </c>
       <c r="D152" t="n">
         <v>0</v>
       </c>
       <c r="E152" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="F152" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G152" t="n">
-        <v>845</v>
+        <v>774</v>
       </c>
     </row>
     <row r="153">
@@ -4542,19 +4542,19 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="D153" t="n">
-        <v>589</v>
+        <v>496</v>
       </c>
       <c r="E153" t="n">
         <v>58</v>
       </c>
       <c r="F153" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G153" t="n">
-        <v>775</v>
+        <v>629</v>
       </c>
     </row>
     <row r="154">
@@ -4596,19 +4596,19 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D155" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E155" t="n">
         <v>8</v>
       </c>
       <c r="F155" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G155" t="n">
-        <v>132</v>
+        <v>89</v>
       </c>
     </row>
     <row r="156">
@@ -4623,19 +4623,19 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D156" t="n">
-        <v>261</v>
+        <v>213</v>
       </c>
       <c r="E156" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F156" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G156" t="n">
-        <v>344</v>
+        <v>264</v>
       </c>
     </row>
     <row r="157">
@@ -4650,7 +4650,7 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="D157" t="n">
         <v>50</v>
@@ -4659,10 +4659,10 @@
         <v>32</v>
       </c>
       <c r="F157" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G157" t="n">
-        <v>499</v>
+        <v>477</v>
       </c>
     </row>
     <row r="158">
@@ -4677,19 +4677,19 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="D158" t="n">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="E158" t="n">
         <v>14</v>
       </c>
       <c r="F158" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G158" t="n">
-        <v>549</v>
+        <v>521</v>
       </c>
     </row>
     <row r="159">
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D161" t="n">
         <v>0</v>
@@ -4767,10 +4767,10 @@
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G161" t="n">
-        <v>139</v>
+        <v>130</v>
       </c>
     </row>
     <row r="162">
@@ -4893,19 +4893,19 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="D166" t="n">
         <v>0</v>
       </c>
       <c r="E166" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G166" t="n">
-        <v>923</v>
+        <v>907</v>
       </c>
     </row>
     <row r="167">
@@ -4920,7 +4920,7 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>551</v>
+        <v>513</v>
       </c>
       <c r="D167" t="n">
         <v>0</v>
@@ -4929,10 +4929,10 @@
         <v>44</v>
       </c>
       <c r="F167" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G167" t="n">
-        <v>651</v>
+        <v>609</v>
       </c>
     </row>
     <row r="168">
@@ -4950,16 +4950,16 @@
         <v>0</v>
       </c>
       <c r="D168" t="n">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="E168" t="n">
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G168" t="n">
-        <v>238</v>
+        <v>186</v>
       </c>
     </row>
     <row r="169">

--- a/outputs/player_points_breakdown.xlsx
+++ b/outputs/player_points_breakdown.xlsx
@@ -1032,19 +1032,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>173</v>
+        <v>227</v>
       </c>
       <c r="D23" t="n">
-        <v>274</v>
+        <v>307</v>
       </c>
       <c r="E23" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="F23" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G23" t="n">
-        <v>539</v>
+        <v>646</v>
       </c>
     </row>
     <row r="24">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -1068,10 +1068,10 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G24" t="n">
-        <v>127</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>16</v>
       </c>
       <c r="F25" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G25" t="n">
-        <v>258</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26">
@@ -1116,13 +1116,13 @@
         <v>18</v>
       </c>
       <c r="D26" t="n">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="E26" t="n">
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G26" t="n">
         <v>32</v>
@@ -1140,19 +1140,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>248</v>
+        <v>284</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="F27" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G27" t="n">
-        <v>328</v>
+        <v>384</v>
       </c>
     </row>
     <row r="28">
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>726</v>
+        <v>813</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1230,10 +1230,10 @@
         <v>34</v>
       </c>
       <c r="F30" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G30" t="n">
-        <v>812</v>
+        <v>903</v>
       </c>
     </row>
     <row r="31">
@@ -1251,16 +1251,16 @@
         <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>177</v>
+        <v>256</v>
       </c>
       <c r="E31" t="n">
         <v>16</v>
       </c>
       <c r="F31" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G31" t="n">
-        <v>240</v>
+        <v>323</v>
       </c>
     </row>
     <row r="32">
@@ -1278,16 +1278,16 @@
         <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>284</v>
+        <v>371</v>
       </c>
       <c r="E32" t="n">
         <v>6</v>
       </c>
       <c r="F32" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G32" t="n">
-        <v>336</v>
+        <v>427</v>
       </c>
     </row>
     <row r="33">
@@ -1305,16 +1305,16 @@
         <v>22</v>
       </c>
       <c r="D33" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E33" t="n">
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G33" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34">
@@ -1332,16 +1332,16 @@
         <v>-2</v>
       </c>
       <c r="D34" t="n">
-        <v>233</v>
+        <v>283</v>
       </c>
       <c r="E34" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F34" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G34" t="n">
-        <v>279</v>
+        <v>349</v>
       </c>
     </row>
     <row r="35">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -1473,10 +1473,10 @@
         <v>8</v>
       </c>
       <c r="F39" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G39" t="n">
-        <v>44</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40">
@@ -1497,13 +1497,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F40" t="n">
         <v>44</v>
       </c>
       <c r="G40" t="n">
-        <v>403</v>
+        <v>415</v>
       </c>
     </row>
     <row r="41">
@@ -1551,13 +1551,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F42" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G42" t="n">
-        <v>447</v>
+        <v>459</v>
       </c>
     </row>
     <row r="43">
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>343</v>
+        <v>430</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
       </c>
       <c r="E64" t="n">
+        <v>64</v>
+      </c>
+      <c r="F64" t="n">
         <v>56</v>
       </c>
-      <c r="F64" t="n">
-        <v>52</v>
-      </c>
       <c r="G64" t="n">
-        <v>451</v>
+        <v>550</v>
       </c>
     </row>
     <row r="65">
@@ -2166,19 +2166,19 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D65" t="n">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="E65" t="n">
         <v>84</v>
       </c>
       <c r="F65" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G65" t="n">
-        <v>395</v>
+        <v>430</v>
       </c>
     </row>
     <row r="66">
@@ -2220,19 +2220,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D67" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E67" t="n">
         <v>64</v>
       </c>
       <c r="F67" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G67" t="n">
-        <v>705</v>
+        <v>709</v>
       </c>
     </row>
     <row r="68">
@@ -2247,19 +2247,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="D68" t="n">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="E68" t="n">
         <v>22</v>
       </c>
       <c r="F68" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G68" t="n">
-        <v>322</v>
+        <v>357</v>
       </c>
     </row>
     <row r="69">
@@ -2274,19 +2274,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>465</v>
+        <v>494</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F69" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G69" t="n">
-        <v>505</v>
+        <v>546</v>
       </c>
     </row>
     <row r="70">
@@ -2301,19 +2301,19 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D70" t="n">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="E70" t="n">
         <v>38</v>
       </c>
       <c r="F70" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G70" t="n">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="71">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -2364,10 +2364,10 @@
         <v>32</v>
       </c>
       <c r="F72" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G72" t="n">
-        <v>109</v>
+        <v>148</v>
       </c>
     </row>
     <row r="73">
@@ -2409,19 +2409,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>214</v>
+        <v>250</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F74" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G74" t="n">
-        <v>294</v>
+        <v>342</v>
       </c>
     </row>
     <row r="75">
@@ -2436,19 +2436,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F75" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G75" t="n">
-        <v>539</v>
+        <v>549</v>
       </c>
     </row>
     <row r="76">
@@ -2493,16 +2493,16 @@
         <v>50</v>
       </c>
       <c r="D77" t="n">
-        <v>464</v>
+        <v>489</v>
       </c>
       <c r="E77" t="n">
         <v>24</v>
       </c>
       <c r="F77" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G77" t="n">
-        <v>586</v>
+        <v>615</v>
       </c>
     </row>
     <row r="78">
@@ -2517,19 +2517,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D78" t="n">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G78" t="n">
-        <v>95</v>
+        <v>156</v>
       </c>
     </row>
     <row r="79">
@@ -2544,19 +2544,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F79" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G79" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="80">
@@ -3246,19 +3246,19 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D105" t="n">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="E105" t="n">
         <v>8</v>
       </c>
       <c r="F105" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G105" t="n">
-        <v>422</v>
+        <v>447</v>
       </c>
     </row>
     <row r="106">
@@ -3300,19 +3300,19 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D107" t="n">
-        <v>297</v>
+        <v>330</v>
       </c>
       <c r="E107" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F107" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G107" t="n">
-        <v>400</v>
+        <v>461</v>
       </c>
     </row>
     <row r="108">
@@ -3327,19 +3327,19 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D108" t="n">
-        <v>160</v>
+        <v>208</v>
       </c>
       <c r="E108" t="n">
         <v>8</v>
       </c>
       <c r="F108" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G108" t="n">
-        <v>216</v>
+        <v>278</v>
       </c>
     </row>
     <row r="109">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>224</v>
+        <v>275</v>
       </c>
       <c r="D110" t="n">
         <v>90</v>
@@ -3390,10 +3390,10 @@
         <v>16</v>
       </c>
       <c r="F110" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G110" t="n">
-        <v>366</v>
+        <v>421</v>
       </c>
     </row>
     <row r="111">
@@ -3543,19 +3543,19 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="F116" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G116" t="n">
-        <v>526</v>
+        <v>553</v>
       </c>
     </row>
     <row r="117">
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>616</v>
+        <v>631</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
@@ -3660,10 +3660,10 @@
         <v>76</v>
       </c>
       <c r="F120" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G120" t="n">
-        <v>736</v>
+        <v>755</v>
       </c>
     </row>
     <row r="121">
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -3687,10 +3687,10 @@
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G121" t="n">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="122">
@@ -3714,10 +3714,10 @@
         <v>8</v>
       </c>
       <c r="F122" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G122" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="123">
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>275</v>
+        <v>356</v>
       </c>
       <c r="D123" t="n">
         <v>0</v>
@@ -3741,10 +3741,10 @@
         <v>24</v>
       </c>
       <c r="F123" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G123" t="n">
-        <v>347</v>
+        <v>432</v>
       </c>
     </row>
     <row r="124">
@@ -3786,19 +3786,19 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D125" t="n">
-        <v>254</v>
+        <v>302</v>
       </c>
       <c r="E125" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F125" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G125" t="n">
-        <v>297</v>
+        <v>366</v>
       </c>
     </row>
     <row r="126">
@@ -3840,19 +3840,19 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="F127" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G127" t="n">
-        <v>606</v>
+        <v>629</v>
       </c>
     </row>
     <row r="128">
@@ -3867,19 +3867,19 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>145</v>
+        <v>195</v>
       </c>
       <c r="D128" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="E128" t="n">
         <v>16</v>
       </c>
       <c r="F128" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G128" t="n">
-        <v>206</v>
+        <v>289</v>
       </c>
     </row>
     <row r="129">
@@ -4464,16 +4464,16 @@
         <v>2</v>
       </c>
       <c r="D150" t="n">
-        <v>299</v>
+        <v>367</v>
       </c>
       <c r="E150" t="n">
         <v>8</v>
       </c>
       <c r="F150" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G150" t="n">
-        <v>349</v>
+        <v>421</v>
       </c>
     </row>
     <row r="151">
@@ -4488,19 +4488,19 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="D151" t="n">
         <v>25</v>
       </c>
       <c r="E151" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F151" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G151" t="n">
-        <v>507</v>
+        <v>541</v>
       </c>
     </row>
     <row r="152">
@@ -4515,19 +4515,19 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>562</v>
+        <v>613</v>
       </c>
       <c r="D152" t="n">
         <v>0</v>
       </c>
       <c r="E152" t="n">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="F152" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G152" t="n">
-        <v>774</v>
+        <v>845</v>
       </c>
     </row>
     <row r="153">
@@ -4542,19 +4542,19 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="D153" t="n">
-        <v>496</v>
+        <v>589</v>
       </c>
       <c r="E153" t="n">
         <v>58</v>
       </c>
       <c r="F153" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G153" t="n">
-        <v>629</v>
+        <v>775</v>
       </c>
     </row>
     <row r="154">
@@ -4596,19 +4596,19 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="D155" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E155" t="n">
         <v>8</v>
       </c>
       <c r="F155" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G155" t="n">
-        <v>89</v>
+        <v>132</v>
       </c>
     </row>
     <row r="156">
@@ -4623,19 +4623,19 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D156" t="n">
-        <v>213</v>
+        <v>261</v>
       </c>
       <c r="E156" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F156" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G156" t="n">
-        <v>264</v>
+        <v>344</v>
       </c>
     </row>
     <row r="157">
@@ -4650,7 +4650,7 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="D157" t="n">
         <v>50</v>
@@ -4659,10 +4659,10 @@
         <v>32</v>
       </c>
       <c r="F157" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G157" t="n">
-        <v>477</v>
+        <v>499</v>
       </c>
     </row>
     <row r="158">
@@ -4677,19 +4677,19 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="D158" t="n">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E158" t="n">
         <v>14</v>
       </c>
       <c r="F158" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G158" t="n">
-        <v>521</v>
+        <v>549</v>
       </c>
     </row>
     <row r="159">
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D161" t="n">
         <v>0</v>
@@ -4767,10 +4767,10 @@
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G161" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="162">
@@ -4893,19 +4893,19 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="D166" t="n">
         <v>0</v>
       </c>
       <c r="E166" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F166" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G166" t="n">
-        <v>907</v>
+        <v>923</v>
       </c>
     </row>
     <row r="167">
@@ -4920,7 +4920,7 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>513</v>
+        <v>551</v>
       </c>
       <c r="D167" t="n">
         <v>0</v>
@@ -4929,10 +4929,10 @@
         <v>44</v>
       </c>
       <c r="F167" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G167" t="n">
-        <v>609</v>
+        <v>651</v>
       </c>
     </row>
     <row r="168">
@@ -4950,16 +4950,16 @@
         <v>0</v>
       </c>
       <c r="D168" t="n">
-        <v>166</v>
+        <v>214</v>
       </c>
       <c r="E168" t="n">
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G168" t="n">
-        <v>186</v>
+        <v>238</v>
       </c>
     </row>
     <row r="169">
